--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
+          <t>https://www.indeed.com/viewjob?jk=22cab9a74c3de505</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data &amp; AI Engineer</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Marketing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=20241d65d96f75a9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Software &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b4743d0857d2b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer V</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
+          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Data Engineer V</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Senior Systems Engineer - Business Analytics Platforms</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pointwest Technologies Corp</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13dcd4834939f146</t>
+          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
+          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=df80db60d78b7884</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Intermediate Quality Software Engineer</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559ccb02cb7d178f</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=1585e663d9eb7646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sprezzatura Management Consulting</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=fa53868c3960897c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef5b1aed9426197</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Sprezzatura Management Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Platform Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer-Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Raiz Federal Credit Union</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,234 +1721,234 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BCS Financial Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a602b929fa90e317</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
+          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MCG Health</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,147 +2061,147 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>MCG Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
+          <t>Health AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
+          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Power BI, DataOps, CI/CD, Azure DevOps, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583b4c9601400970</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=f59126b80c7ef8d0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Star Schema, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Snowflake, Oracle, Dimensional Modeling, Star Schema, ETL, ELT, Pentaho</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Senior Software Engineer - Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior System Engineering - Engineering Operations</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda7123f0312159f</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior .NET Developer - Full-time (Working from Office)</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Harbinger Motors Inc.</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,94 +3471,94 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1042fb894a308b35</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect / Data Modeling Consultant</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Intratek Computer</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior .NET Developer - Full-time (Working from Office)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Full Stack Intern</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=82a069c2dfe402ab</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d57f388e905047</t>
+          <t>https://www.indeed.com/viewjob?jk=81d9825726720fc7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Automated Tester/Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65bbafc6442ac9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Data Architect / Data Modeling Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Intratek Computer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,435 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Octapharma</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sr. Software Automated Tester/Developer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pyramid Systems Inc</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f65bbafc6442ac9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Labcorp</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Rocket55</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer II</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D.R. Horton</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=61d632e85736717d</t>
         </is>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cab9a74c3de505</t>
+          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Sr. Marketing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data &amp; AI Engineer</t>
+          <t>Senior Software &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,112 +636,112 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20241d65d96f75a9</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software &amp; Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
+          <t>https://www.indeed.com/viewjob?jk=58f301bd952067c4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
+          <t>https://www.indeed.com/viewjob?jk=bba1c0ac588dfc09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec4126d57c004c0</t>
         </is>
       </c>
     </row>
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df80db60d78b7884</t>
+          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1585e663d9eb7646</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
@@ -1208,20 +1208,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa53868c3960897c</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trafigura</t>
+          <t>Sprezzatura Management Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
+          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Platform Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef5b1aed9426197</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sprezzatura Management Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,172 +1721,172 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MCG Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
+          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Health AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,172 +2036,172 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MCG Health</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Health AI Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Senior Software Engineer - Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59126b80c7ef8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,129 +2701,129 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack Engineer</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, GCP, Dataflow, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,147 +3111,147 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f836a90a9a6c4031</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Data Architect / Data Modeling Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Intratek Computer</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,129 +3436,129 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior .NET Developer - Full-time (Working from Office)</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571f6ef27368da0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Octapharma</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Rocket55</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, DynamoDB, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82a069c2dfe402ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d9825726720fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,602 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Architect / Data Modeling Consultant</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Intratek Computer</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Teaneck, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Teaneck, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Teaneck, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Teaneck, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Teaneck, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr. Data Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Octapharma</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr. Software Automated Tester/Developer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Pyramid Systems Inc</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f65bbafc6442ac9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Labcorp</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Rocket55</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer II</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>D.R. Horton</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer – Alteryx Platform Owner / Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61d632e85736717d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4eedea720bd23228</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data &amp; AI Engineer</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software &amp; Data Engineer</t>
+          <t>Sr. Marketing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>Senior Software &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f301bd952067c4</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineer V</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba1c0ac588dfc09</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Systems Engineer - Business Analytics Platforms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec4126d57c004c0</t>
+          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer V</t>
+          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Business Analytics Platforms</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
+          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
+          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Sprezzatura Management Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trafigura</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
+          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,46 +1287,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sprezzatura Management Consulting</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer, NYT Cooking</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=31ad8aa9682337b7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Health AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Health AI Engineer</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Senior Software Engineer - Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,59 +3086,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Data Architect / Data Modeling Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Intratek Computer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect / Data Modeling Consultant</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intratek Computer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
         </is>
       </c>
     </row>
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Octapharma</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Rocket55</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rocket55</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3820,41 +3820,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
         </is>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ce88ab29e1bd168</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trafigura</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Sprezzatura Management Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Platform Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sprezzatura Management Consulting</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Data Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,29 +1396,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, NYT Cooking</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ad8aa9682337b7</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>AmpliFI Loyalty Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>MCG Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,129 +1861,129 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MCG Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Health AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jupiter, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0375170793a22d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
+          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Endeavor Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4d0ffada167292</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Data Scientist - AI Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,77 +3076,77 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Scala, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdeb66468dd0add</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Architect / Data Modeling Consultant</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Intratek Computer</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rocket55</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Data Architect / Data Modeling Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Intratek Computer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,365 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Developer II</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Octapharma</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Labcorp</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Rocket55</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer II</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D.R. Horton</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
         </is>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Technical Data Security Architect- Remote (Anywhere in the U.S.)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>GuidePoint Security</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Azure, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c8acbe5f71af378</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data &amp; AI Engineer</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software &amp; Data Engineer</t>
+          <t>Sr. Marketing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>Senior Software &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer V</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8220b39cfe7da8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed5e5d6e7ec548f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Sprezzatura Management Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Platform Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trafigura</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Impala, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422a205347b81a58</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sprezzatura Management Consulting</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AmpliFI Loyalty Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d5413692a768ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,42 +1511,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d72bea8288f357ee</t>
+          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
         </is>
       </c>
     </row>
@@ -1558,257 +1558,257 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MCG Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Senior Software Engineer - Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Endeavor Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298c4bfe00214f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevSecOps Platform Engineer, AI Automation</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,49 +2351,49 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,15 +2403,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,137 +2421,137 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack Engineer</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4d0ffada167292</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist - AI Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Scala, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdeb66468dd0add</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4d0ffada167292</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Platform</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Scala, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdeb66468dd0add</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,94 +3366,94 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>First United Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Data Architect / Data Modeling Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Intratek Computer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect / Data Modeling Consultant</t>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Intratek Computer</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
         </is>
       </c>
     </row>
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Octapharma</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rocket55</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rocket55</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4065,111 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Worth AI</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
         </is>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data &amp; AI Engineer</t>
+          <t>Senior Software &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software &amp; Data Engineer</t>
+          <t>Senior Systems Engineer - Business Analytics Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
+          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Business Analytics Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
+          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Copilot Studio Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Exaways Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb78da13ef87da9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
@@ -993,60 +993,60 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sprezzatura Management Consulting</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2068100094fd3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0950591f503ca967</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a79496f7a592b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Sr Data Quality Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, NoSQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,94 +1371,94 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Data Architect - Advanced</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
+          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevSecOps Platform Engineer, AI Automation</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer - Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,77 +2026,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,129 +2106,129 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Data Architect - Intermediate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Foundations)</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4d0ffada167292</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Platform</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Scala, Kafka, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdeb66468dd0add</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,384 +2796,384 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b332d7295b6f32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>First United Bank</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect / Data Modeling Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Intratek Computer</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6fae39e910d8c57</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rocket55</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,52 +4021,1697 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Burlington Stores</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Edgewater Park, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect Consultant</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CG Infinity</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Sugar Land, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Incyte Corporation</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Chadds Ford, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>First United Bank</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Rocket55</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer II</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D.R. Horton</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Worth AI</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Integrations</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Worth AI</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
         <is>
           <t>Orlando, FL, US USA</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sr. Data Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Octapharma</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Labcorp</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Developer II</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Entry-level Moment AWS Contact Center Developer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Per Scholas</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5657fb12c61599a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Per Scholas</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02369e600e25dc94</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Per Scholas</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1bc0b35c1a8f947</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Per Scholas</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f76045b3e1a34f</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Per Scholas</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13e7ce1cf6e3d127</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Per Scholas</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a641c5288812497c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL/Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,84 +566,84 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4ed6016f6f36df</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=b342f596ec91b873</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software &amp; Data Engineer</t>
+          <t>Senior Azure Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c2f00c8f14faf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Business Analytics Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,46 +657,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Event Hubs, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
+          <t>https://www.indeed.com/viewjob?jk=a12b68897c303e12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Cloud Data Products &amp; Analytic Enablement</t>
+          <t>Senior Software &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8824834cc316357</t>
+          <t>https://www.indeed.com/viewjob?jk=a6aeb6534e09ea2c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>S3, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e95aa7f426e979</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Copilot Studio Architect</t>
+          <t>Senior Systems Engineer - Business Analytics Platforms</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Exaways Corporation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb78da13ef87da9</t>
+          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Copilot Studio Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Exaways Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb78da13ef87da9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5883ce98bd3b809</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,182 +1151,182 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff0969407ce52a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Quality Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8363d4aab2e6b33f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Observability Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51363c57ca4af5f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevSecOps Platform Engineer, AI Automation</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect - Advanced</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2598e893f85ae2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,112 +2026,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Oracle, SQL Server, MySQL, MongoDB, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc008231630670</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Hillpointe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Winter Park, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=df04f5f46c0676e7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4303a949ff0206</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99ee79a934f0166</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ef21a1e4293fd</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect - Intermediate</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a36f9ca1924521</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Hadoop, Hive, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=e88a7bf9cdf22da2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,77 +2796,77 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae21c352f885d87b</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3a97c6dacfd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data, API &amp; Platform Integration)</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f645727415a8c94</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>First United Bank</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,29 +5001,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rocket55</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
+          <t>https://www.indeed.com/viewjob?jk=c14e4d10c6e22519</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
+          <t>https://www.indeed.com/viewjob?jk=afb67d72c9eae1bd</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=578e74dac35a2574</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>First United Bank</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Octapharma</t>
+          <t>Rocket55</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4dc84fd3a2c0c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=241ee8dad1872af1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Business Intelligence Developer II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1caba29237e465</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752a175f328041d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d0c56dc9911793</t>
+          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de604a499b6e351</t>
+          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Senior Software Engineer - Integrations</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5477f4e7c8ef39b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Entry-level Moment AWS Contact Center Developer</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Teaneck, NJ, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bd9fb18e41b893</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Per Scholas</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,24 +5491,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5657fb12c61599a9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5657fb12c61599a9</t>
+          <t>https://www.indeed.com/viewjob?jk=02369e600e25dc94</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02369e600e25dc94</t>
+          <t>https://www.indeed.com/viewjob?jk=d1bc0b35c1a8f947</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1bc0b35c1a8f947</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f76045b3e1a34f</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f76045b3e1a34f</t>
+          <t>https://www.indeed.com/viewjob?jk=13e7ce1cf6e3d127</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
+          <t>Technical Instructor (AWS Machine Learning)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5675,41 +5675,6 @@
         </is>
       </c>
       <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13e7ce1cf6e3d127</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Technical Instructor Instructor (AWS Machine Learning)</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Per Scholas</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a641c5288812497c</t>
         </is>

--- a/results/job_matches_2026-05-22.xlsx
+++ b/results/job_matches_2026-05-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer – Healthcare Systems &amp; Automation (On-Site Brooklyn, NY)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>True Care</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
+          <t>https://www.indeed.com/viewjob?jk=e93b9f3b83186e48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Business Analytics Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
+          <t>https://www.indeed.com/viewjob?jk=dad3302c1d85587a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Engineer - Business Analytics Platforms</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=dee9004c615d6323</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e917c30ee7d0c2a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Agentic AI</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Light &amp; Wonder</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa49faad8ad49a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Copilot Studio Architect</t>
+          <t>Senior Data Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Exaways Corporation</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb78da13ef87da9</t>
+          <t>https://www.indeed.com/viewjob?jk=04a6df7b92992269</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Copilot Studio Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Exaways Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb78da13ef87da9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
+          <t>https://www.indeed.com/viewjob?jk=b3ac500b7f8a3d0c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr.Specialist , Software Development Engineering</t>
+          <t>Senior ML Ops Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, Scala, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6329c226be016e1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1a78888adf4b70</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Sr.Specialist , Software Development Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
+          <t>https://www.indeed.com/viewjob?jk=d675ec9acd758b5a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
+          <t>https://www.indeed.com/viewjob?jk=08ce5092cd224c52</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c339fd3829743220</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer, Energy, Sales, &amp; Services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Databricks, Data Lake Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a5e5e0026531</t>
+          <t>https://www.indeed.com/viewjob?jk=3666b5644b9c9923</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Migration Architect</t>
+          <t>Senior Software Engineer - Data Integration &amp; JVM Ecosystem</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Kafka, Kafka Connect, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff0969407ce52a</t>
+          <t>https://www.indeed.com/viewjob?jk=c26241d9e133498f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ebb2a9d9abf85a2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - DevSecOps</t>
+          <t>Senior Migration Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff0969407ce52a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3175e4ce5d95b8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform Engineer - DevSecOps</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
+          <t>https://www.indeed.com/viewjob?jk=363a8bb5bcd93f17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jr Software Engineer (Automation &amp; Tools)</t>
+          <t>Data Scientist II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,139 +1431,139 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, Dask</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d29470f2d0a62b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>Analytics Engineer, Feature Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Spark, Scala, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=dece9a64d002f7db</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fd194e6f8429f5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Jr Software Engineer (Automation &amp; Tools)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
+          <t>https://www.indeed.com/viewjob?jk=586f4250ce0182d7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>AI ML Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=c616dee9f9248ca8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9e3b948b202c9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8a3cd3d79aed67</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PL Ops - Data Engineer (Worcester or Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=4a15f9e5c8fce882</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
+          <t>https://www.indeed.com/viewjob?jk=837099917f2a5dec</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
+          <t>https://www.indeed.com/viewjob?jk=afb98e31dbf7c26e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=0520872b1a01b2e9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
+          <t>https://www.indeed.com/viewjob?jk=5205a09ebe414c2e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d22035552ebbc26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Citizens Business Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
+          <t>https://www.indeed.com/viewjob?jk=746fc72a8d6e25af</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
+          <t>https://www.indeed.com/viewjob?jk=f67deeebae08ffda</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
+          <t>https://www.indeed.com/viewjob?jk=05e8bfc8a8d4b75c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=2488c8c958f34004</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Financial Transactions &amp; Automation</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wiliot</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83c7c7e8d1a81f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens Business Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
+          <t>https://www.indeed.com/viewjob?jk=d58fe2f79c50231d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevSecOps Platform Engineer, AI Automation</t>
+          <t>Eng., Digital Dist &amp; Ent Eng</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Zookeeper, Splunk, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8afa0d739e09ad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7a99e7f4abccf3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Associate Software Developer Intern (AI and Cloud) - Local to Indiana</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hillpointe</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Winter Park, FL, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, PostgreSQL, Data Modeling, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3a3937b7571485</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69372e3345faef</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df04f5f46c0676e7</t>
+          <t>https://www.indeed.com/viewjob?jk=05e5a702a64a8b3b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CompTactics, LLC</t>
+          <t>Wiliot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
+          <t>https://www.indeed.com/viewjob?jk=164acb50d12acaca</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee3449ed9ca504d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
+          <t>https://www.indeed.com/viewjob?jk=44b17327ccbdd128</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer IV</t>
+          <t>DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
+          <t>https://www.indeed.com/viewjob?jk=093594d135187bdb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=df04f5f46c0676e7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Identity Security Metrics Consultant &amp; Databricks Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CompTactics, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, ETL, Talend, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
+          <t>https://www.indeed.com/viewjob?jk=db5e54fae6b0638b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
+          <t>https://www.indeed.com/viewjob?jk=f07674c9e7674b7f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (HYBRID in MA or REMOTE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=154874ff0ca10323</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer IV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
+          <t>https://www.indeed.com/viewjob?jk=047dbbdf9319bbe1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
+          <t>https://www.indeed.com/viewjob?jk=0b7d8eadc95aa5ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data and AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
+          <t>https://www.indeed.com/viewjob?jk=1551268778a617f5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de96b3860fd283</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbe170ed826dedf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20797696d8c96d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Kubernetes, Python</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88a7bf9cdf22da2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5366178ee570d26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Golang Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Webcreek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, BigQuery, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=74fe95ce9dd80535</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>Data and AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Data Modeling, Power BI, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
+          <t>https://www.indeed.com/viewjob?jk=efb47d2533a7c899</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II (MA BASED OR REMOTE)</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Hadoop, Hive, Spark, Scala, Kafka, MLOps, MLflow, CI/CD, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e88a7bf9cdf22da2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Junior SQL Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
+          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Golang Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=61f6cdaedc4aa6b4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior SQL Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Vertex AI, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,164 +2911,164 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3098dd926c1d2e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=cba127e0361a9979</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d32f2b5f65dde91</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (MA BASED OR REMOTE)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>First Help Financial</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
+          <t>https://www.indeed.com/viewjob?jk=89e0515b86de94cd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Datavant</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e19e3ed0f63ef43</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ponte Vedra, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
+          <t>https://www.indeed.com/viewjob?jk=93f255d27a698cf1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Zookeeper, Spark, Scala, Kafka, Snowflake, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
+          <t>https://www.indeed.com/viewjob?jk=10d6478154035bc2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>APCO Holdings</t>
+          <t>First Help Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, MySQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
+          <t>https://www.indeed.com/viewjob?jk=6b04d49c0812cd3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer - Ingestion &amp; Streaming Frameworks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f6fac40c8e61d9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Ponte Vedra, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
+          <t>https://www.indeed.com/viewjob?jk=b267a98b6ca3ae0d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
+          <t>https://www.indeed.com/viewjob?jk=6eddd6eef0cda463</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>APCO Holdings</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff857bf8cc81feb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4850b4115d1ec83d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
+          <t>https://www.indeed.com/viewjob?jk=157f075ed24c2620</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
+          <t>https://www.indeed.com/viewjob?jk=dba16b9e8383c743</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
+          <t>https://www.indeed.com/viewjob?jk=4050251046e4b967</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
+          <t>https://www.indeed.com/viewjob?jk=283ba40052ed9a1c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
+          <t>https://www.indeed.com/viewjob?jk=85d1291f06b8c10e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
+          <t>https://www.indeed.com/viewjob?jk=0344e8d4175ecc98</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1639ef75f537fb4f</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
+          <t>https://www.indeed.com/viewjob?jk=2fef9ac1a48db083</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e597aea8ce709e59</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
+          <t>https://www.indeed.com/viewjob?jk=cf826e02da58d16b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ef975bb0a407c9a5</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
+          <t>https://www.indeed.com/viewjob?jk=c755fa6fd83bf785</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
+          <t>https://www.indeed.com/viewjob?jk=485880f691afee1a</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
+          <t>https://www.indeed.com/viewjob?jk=1deac2472afd5e93</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
+          <t>https://www.indeed.com/viewjob?jk=6819e25ce42fd9ee</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a950d3a005b7339</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
+          <t>https://www.indeed.com/viewjob?jk=dad01fbd8538d636</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
+          <t>https://www.indeed.com/viewjob?jk=403b5f974e53992d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
+          <t>https://www.indeed.com/viewjob?jk=4af30e3581decda0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d5a1e72689b6a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
+          <t>https://www.indeed.com/viewjob?jk=d355e8488073d739</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
+          <t>https://www.indeed.com/viewjob?jk=3f953dc4994c3667</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
+          <t>https://www.indeed.com/viewjob?jk=7149315a218fcccc</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
+          <t>https://www.indeed.com/viewjob?jk=b01d3b0fc61fac79</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce02ae38d2e3daf2</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
+          <t>https://www.indeed.com/viewjob?jk=34986a8a22d98000</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
+          <t>https://www.indeed.com/viewjob?jk=0f53f1e2cdee1071</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2b98a4ab60e977</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
+          <t>https://www.indeed.com/viewjob?jk=aef0c7eeacdab1d3</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eb216f51c52c79</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
+          <t>https://www.indeed.com/viewjob?jk=89fcdea25a777721</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=064cd527ea7f6255</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
+          <t>https://www.indeed.com/viewjob?jk=58e22727bb3d1952</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0a6c8b5f8155e9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
+          <t>https://www.indeed.com/viewjob?jk=eac865b8c888a303</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d737907986f22b</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
+          <t>https://www.indeed.com/viewjob?jk=0006df8bf0dbecbc</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fce945869a48d03</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa1efff4a88791</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c703a8545afdbf64</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e2926b6cfb0d38</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
+          <t>https://www.indeed.com/viewjob?jk=45b135eda3a89ca4</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
+          <t>https://www.indeed.com/viewjob?jk=7478cd6b966a3b75</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
+          <t>https://www.indeed.com/viewjob?jk=12348259f08f22b7</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5afb48e66b9b67b6</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
+          <t>https://www.indeed.com/viewjob?jk=474e2ea897e2c7ef</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
+          <t>https://www.indeed.com/viewjob?jk=d0298e0a093f1e02</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
+          <t>https://www.indeed.com/viewjob?jk=62f956ac3c337b34</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer/Assoc. Commercial Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chadds Ford, PA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
+          <t>https://www.indeed.com/viewjob?jk=036d5a6fa300b4e9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14e4d10c6e22519</t>
+          <t>https://www.indeed.com/viewjob?jk=1996653eaea87251</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Customer Solutions Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Rocket Software</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, Jenkins, AWS CodePipeline, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb67d72c9eae1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8dcefab27eeb14db</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578e74dac35a2574</t>
+          <t>https://www.indeed.com/viewjob?jk=fa2aac8c72a4cdad</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c14e4d10c6e22519</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>First United Bank</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
+          <t>https://www.indeed.com/viewjob?jk=afb67d72c9eae1bd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
+          <t>https://www.indeed.com/viewjob?jk=578e74dac35a2574</t>
         </is>
       </c>
     </row>
@@ -5298,17 +5298,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec6348a1a771646</t>
+          <t>https://www.indeed.com/viewjob?jk=d530d2af319399b5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>First United Bank</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add45f9e195492ab</t>
+          <t>https://www.indeed.com/viewjob?jk=795069cfefc40dca</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Enterprise Data Architect Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2053b2017dbd159</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ef7ab061c33cc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations</t>
+          <t>Data Engineer/Assoc. Commercial Data Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chadds Ford, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, RDS, Kafka, PostgreSQL, ETL</t>
+          <t>ECS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7845c99df3c7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8482aad5503f7982</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Snowflake, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3be062ecd99df873</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
+          <t>Enterprise Data Modeler / Data Architect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>STERIS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,192 +5491,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5657fb12c61599a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Per Scholas</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02369e600e25dc94</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Per Scholas</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1bc0b35c1a8f947</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Per Scholas</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f76045b3e1a34f</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Per Scholas</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13e7ce1cf6e3d127</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Technical Instructor (AWS Machine Learning)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Per Scholas</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, MLOps, CI/CD, Git, CloudWatch, CloudTrail</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a641c5288812497c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdede7f9e82d0fd</t>
         </is>
       </c>
     </row>
